--- a/AAII_Financials/Quarterly/OWL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OWL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="92">
   <si>
     <t>OWL</t>
   </si>
@@ -656,123 +656,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
@@ -782,88 +783,91 @@
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>753100</v>
+      </c>
+      <c r="E8" s="3">
         <v>753800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>755600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>728000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>703100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>683500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>631400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>600900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>549800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>513300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>494000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>429700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>416900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>391000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>395500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>371000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>327200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>276000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>288500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>247900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>179300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>108200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>106000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>54000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>40500</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>0</v>
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD8" s="3">
         <v>0</v>
@@ -871,53 +875,56 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>313500</v>
+      </c>
+      <c r="E9" s="3">
         <v>326600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>292700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>308500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>288400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>290300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>255400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>252400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>207300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>205200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>205300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>168600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>163200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>153900</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -960,53 +967,56 @@
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>439600</v>
+      </c>
+      <c r="E10" s="3">
         <v>427200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>462900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>419500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>414800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>393200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>375900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>348500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>342600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>308100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>288800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>261000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>253800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>237100</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1049,8 +1059,11 @@
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1082,8 +1095,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1171,8 +1185,11 @@
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1260,88 +1277,91 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E14" s="3">
         <v>84500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>47600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>119900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>88000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>132000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>73700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>61400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>31800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>24200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>56500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>56600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>37500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>46200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-12700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>10400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>9600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>17500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>4100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>51400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>900</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1349,88 +1369,91 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>85500</v>
+      </c>
+      <c r="E15" s="3">
         <v>84500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>87400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>92700</v>
-      </c>
-      <c r="G15" s="3">
-        <v>89500</v>
       </c>
       <c r="H15" s="3">
         <v>89500</v>
       </c>
       <c r="I15" s="3">
+        <v>89500</v>
+      </c>
+      <c r="J15" s="3">
         <v>76700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>68700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>56700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>56200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>56800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>56700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>115900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>70900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>64700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>65800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>64900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>61500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>46400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>46200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>21300</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>0</v>
+      <c r="AA15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD15" s="3">
         <v>0</v>
@@ -1438,8 +1461,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1468,86 +1494,87 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>535100</v>
+      </c>
+      <c r="E17" s="3">
         <v>541400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>510600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>522000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>499600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>483900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>442000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>399200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>345900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>329900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>330300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>282800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>326900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>280800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>367500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>368600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>337400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>298700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>223800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>171500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1310600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>62800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>151400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>57900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>47900</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1557,86 +1584,89 @@
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>218000</v>
+      </c>
+      <c r="E18" s="3">
         <v>212400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>245000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>206000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>203500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>199600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>189300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>201700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>204000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>183400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>163700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>146800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>90100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>110200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>28000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-10200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-22700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>64700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>76400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1131300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>45400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-45400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1646,8 +1676,11 @@
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1679,8 +1712,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1699,54 +1733,54 @@
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
         <v>20400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>6300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>14700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>10500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-19300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>21800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>7600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-90400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-325500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-479500</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
@@ -1756,8 +1790,8 @@
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
+      <c r="AB20" s="3">
+        <v>0</v>
       </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
@@ -1768,86 +1802,89 @@
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>303400</v>
+      </c>
+      <c r="E21" s="3">
         <v>297000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>332300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>298600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>293000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>289100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>245600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>264000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>263800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>224900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>210100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>201500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>206400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>179100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>74900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>67000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>76700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>46600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>20800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-202700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1589300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>45500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-45400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1857,88 +1894,91 @@
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>47700</v>
+      </c>
+      <c r="E22" s="3">
         <v>43900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>40900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>42400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>42000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>38500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>32600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>34100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>32700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>22500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>18500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>19700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>19200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>18400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>12800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>15000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>15100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>12800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>9500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>6100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>5800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>5900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>5800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>6100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>6000</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>0</v>
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
@@ -1946,86 +1986,89 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>70900</v>
+      </c>
+      <c r="E23" s="3">
         <v>95800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>167800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>55300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>84500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>40300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>74100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>112100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>156300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>126800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>84300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>74200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>39400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>48500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-14100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-28000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-35200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-255200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1616500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>39500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-51200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-9900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-13400</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
@@ -2035,88 +2078,91 @@
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E24" s="3">
         <v>16200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>17000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>13800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>12800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>18200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>14800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>10700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-5900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-4100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-5000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-21800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-14400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-29200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>200</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
       <c r="Z24" s="3">
         <v>0</v>
       </c>
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>0</v>
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD24" s="3">
         <v>0</v>
@@ -2124,8 +2170,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2213,86 +2262,89 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>60700</v>
+      </c>
+      <c r="E26" s="3">
         <v>79600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>150700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>47400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>70700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>36700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>71100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>99300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>138100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>112000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>81200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>63500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>34000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>42000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-10000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-9100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-22900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-13400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-240800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1587300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>39300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-51200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-9900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-13300</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2302,86 +2354,89 @@
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E27" s="3">
         <v>15500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>47700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>17400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>20700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>29800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>33900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>25100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>18100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>15100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>12900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>8300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-11800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-53300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-362300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>39400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-49700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-8600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-12400</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2391,8 +2446,11 @@
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2480,8 +2538,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2569,8 +2630,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2658,8 +2722,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2747,8 +2814,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2767,54 +2837,54 @@
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
         <v>-20400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-6300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-14700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-10500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>19300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-21800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-7600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>90400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>325500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>479500</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
@@ -2824,8 +2894,8 @@
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
+      <c r="AB32" s="3">
+        <v>0</v>
       </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
@@ -2836,86 +2906,89 @@
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E33" s="3">
         <v>15500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>47700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>17400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>20700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>29800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>33900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>25100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>18100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>15100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>12900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>8300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-11800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-53300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-362300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>39400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-49700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-8600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-12400</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2925,8 +2998,11 @@
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3014,86 +3090,89 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E35" s="3">
         <v>15500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>47700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>17400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>20700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>29800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>33900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>25100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>18100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>15100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>12900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>8300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-11800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-53300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-362300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>39400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-49700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-8600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-12400</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3103,91 +3182,94 @@
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3197,8 +3279,11 @@
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3230,8 +3315,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3263,77 +3349,78 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>169100</v>
+      </c>
+      <c r="E41" s="3">
         <v>190500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>194500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>137300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>117600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>97600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>152100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>115900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>436800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>155800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>104200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>76700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>41300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>37900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>68100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>39500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>48700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>186000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>42600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>138900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>436000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>8600</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3352,8 +3439,11 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3441,77 +3531,80 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1034900</v>
+      </c>
+      <c r="E43" s="3">
         <v>1075300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1070700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1020800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>999100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1055200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>948900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>940900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>843900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>801800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>800100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>790500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>784500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>761500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>357900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>368100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>281900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>211600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>224600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>184300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>147500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>100300</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3521,8 +3614,8 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD43" s="3">
         <v>0</v>
@@ -3530,8 +3623,11 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3574,8 +3670,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3619,8 +3715,11 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3663,30 +3762,30 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3">
         <v>6100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>8500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>8900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>7100</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3708,53 +3807,56 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1265000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1307400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1298700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1203400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1165000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1182000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1118700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1077300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1294200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>966600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>911400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>876100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>832700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>807000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -3788,8 +3890,8 @@
       <c r="AB46" s="3">
         <v>0</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>3</v>
+      <c r="AC46" s="3">
+        <v>0</v>
       </c>
       <c r="AD46" s="3" t="s">
         <v>3</v>
@@ -3797,71 +3899,74 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>563700</v>
+      </c>
+      <c r="E47" s="3">
         <v>511000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>484400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>513900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>485900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>466100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>486900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>456200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>431100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>357800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>344300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>353100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>361900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>346500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>329200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>201200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>44800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>16400</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V47" s="3">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W47" s="3">
         <v>300600</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3886,77 +3991,80 @@
       <c r="AE47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>676700</v>
+      </c>
+      <c r="E48" s="3">
         <v>677400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>675100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>666300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>536900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>543500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>512800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>471200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>459900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>430400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>416600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>369900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>359000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>315100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>295600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>278800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>119900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>112400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>94000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>69900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>61100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>16100</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3966,8 +4074,8 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC48" s="3">
-        <v>0</v>
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD48" s="3">
         <v>0</v>
@@ -3975,74 +4083,77 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8343300</v>
+      </c>
+      <c r="E49" s="3">
         <v>8428700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8513300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8600600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8693300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8782700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7602200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7678900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6403500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6278000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6334200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6392800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>6423800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6539700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6610600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6675200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6741100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6682100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6743700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5713900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5760100</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4055,8 +4166,8 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC49" s="3">
-        <v>0</v>
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD49" s="3">
         <v>0</v>
@@ -4064,8 +4175,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4153,8 +4267,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4242,77 +4359,80 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E52" s="3">
         <v>20600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>26900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>59800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>24300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>41400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>16900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>16200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>13900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>20200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>757200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>733300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>683300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>648900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>636000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>514500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>442200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>16400</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4331,8 +4451,11 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4420,77 +4543,80 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12334200</v>
+      </c>
+      <c r="E54" s="3">
         <v>12414700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12467700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12469300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12279000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12286200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10992500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10751900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9660600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8985500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8817600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8771300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8751900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8762900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8893100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8792300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>8418700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>8360900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>8266400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7450100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6872200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>149000</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4509,8 +4635,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4542,8 +4671,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4575,77 +4705,78 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>164500</v>
+      </c>
+      <c r="E57" s="3">
         <v>176300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>159100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>178300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>145100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>226000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>158300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>197200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>139000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>143900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>129400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>127200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>125200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>143600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>126600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>147200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>90500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>85900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>68300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>81200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>110200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>62400</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4655,8 +4786,8 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC57" s="3">
-        <v>0</v>
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD57" s="3">
         <v>0</v>
@@ -4664,53 +4795,56 @@
       <c r="AE57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E58" s="3">
         <v>46800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>62400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>15600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>13900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>24000</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>2000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>19100</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>3200</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>9800</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -4726,15 +4860,15 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X58" s="3">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y58" s="3">
         <v>113100</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4753,77 +4887,80 @@
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E59" s="3">
         <v>4300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>9700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>549500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>483300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>253800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>182700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>244100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>241300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>189500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>195100</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4842,53 +4979,56 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>638400</v>
+      </c>
+      <c r="E60" s="3">
         <v>517100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>751000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>652900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>503500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>492100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>590000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>549500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>384900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>327800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>509500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>429200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>350900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>311000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -4922,8 +5062,8 @@
       <c r="AB60" s="3">
         <v>0</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>3</v>
+      <c r="AC60" s="3">
+        <v>0</v>
       </c>
       <c r="AD60" s="3" t="s">
         <v>3</v>
@@ -4931,77 +5071,80 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4313500</v>
+      </c>
+      <c r="E61" s="3">
         <v>4309700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3800100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3761300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3633800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3575400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2978800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2902000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2796200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2387600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2000800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2046500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2057600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2016400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1624800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1526000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1413200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1412500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1174200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>683600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>683300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>246700</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -5020,74 +5163,77 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1730500</v>
+      </c>
+      <c r="E62" s="3">
         <v>1760200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1822700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1838500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1743400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1749200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1580700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1380800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1227600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1065300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>995000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>941400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>935700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>926200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>41800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>41400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>49900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>44400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>49000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>50400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>48600</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5109,8 +5255,11 @@
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5198,8 +5347,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5287,8 +5439,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5376,77 +5531,80 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6720400</v>
+      </c>
+      <c r="E66" s="3">
         <v>6627100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6413500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6290800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5919200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5857000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5186400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4872900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4442400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3813900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3539700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3453100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3380300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3293600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7288400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7137700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6796000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>6744400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>6602800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6034600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5772500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>626300</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5465,8 +5623,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5498,8 +5659,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5587,8 +5749,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5676,8 +5841,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5765,8 +5933,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5854,77 +6025,80 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1888500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1744500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1609500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1507700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1367600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1244200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1141600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1054200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-982700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-923000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-882900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-837100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-788500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-738900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-689300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-638300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-591700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-549800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-497500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-463600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-397200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-477400</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5943,8 +6117,11 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6032,8 +6209,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6121,8 +6301,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6210,77 +6393,80 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1996500</v>
+      </c>
+      <c r="E76" s="3">
         <v>2099600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2205400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2295900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2350800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2335500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2127800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2003800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1746900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1646100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1528200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1541800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1571400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1589700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1604700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1654600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1622700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1616500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1663600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1415600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1099800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-477400</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6299,8 +6485,11 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6388,91 +6577,94 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6482,86 +6674,89 @@
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E81" s="3">
         <v>15500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>47700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>17400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>20700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>29800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>33900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>25100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>18100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>15100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>12900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>8300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-11800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-53300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-362300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>39400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-49700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-8600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-12400</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6571,8 +6766,11 @@
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6604,43 +6802,44 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E83" s="3">
         <v>5600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>2800</v>
       </c>
       <c r="I83" s="3">
         <v>2800</v>
       </c>
       <c r="J83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K83" s="3">
         <v>2900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1600</v>
-      </c>
-      <c r="N83" s="3">
-        <v>200</v>
       </c>
       <c r="O83" s="3">
         <v>200</v>
@@ -6649,43 +6848,43 @@
         <v>200</v>
       </c>
       <c r="Q83" s="3">
+        <v>200</v>
+      </c>
+      <c r="R83" s="3">
         <v>66300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>66100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>65100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>61700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>46600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>46400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>21500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>100</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
-      </c>
       <c r="Z83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AA83" s="3">
         <v>200</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>0</v>
+      <c r="AB83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD83" s="3">
         <v>0</v>
@@ -6693,8 +6892,11 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6782,8 +6984,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6871,8 +7076,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6960,8 +7168,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7049,8 +7260,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7138,86 +7352,89 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>461300</v>
+      </c>
+      <c r="E89" s="3">
         <v>102800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>382900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>433100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>422500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>17600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>324000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>326000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>302300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>47200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>308300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>281700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>238100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>121000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>276100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>206900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>152300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>93200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>154300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>109100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>17700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>22800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>6300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7227,8 +7444,11 @@
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7260,73 +7480,74 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-23700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-10600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-13300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-32900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-33500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-18500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-23900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-9500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-18400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-200</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-300</v>
       </c>
       <c r="Y91" s="3">
         <v>-300</v>
@@ -7335,13 +7556,13 @@
         <v>-300</v>
       </c>
       <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>0</v>
+        <v>-300</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
@@ -7349,8 +7570,11 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7438,8 +7662,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7527,73 +7754,76 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-54700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-27100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>13100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-21500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-65200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-197000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-46300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-441800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-134700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-15300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-23900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-37200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-22500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-34400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-139300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-170800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-152500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-22600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-324800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-296700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-977100</v>
-      </c>
-      <c r="X94" s="3">
-        <v>-300</v>
       </c>
       <c r="Y94" s="3">
         <v>-300</v>
@@ -7602,13 +7832,13 @@
         <v>-300</v>
       </c>
       <c r="AA94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC94" s="3">
-        <v>0</v>
+        <v>-300</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD94" s="3">
         <v>0</v>
@@ -7616,8 +7846,11 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7649,68 +7882,69 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>155400</v>
+      </c>
+      <c r="E96" s="3">
         <v>150500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>149400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>146500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>140800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>110000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>108200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>101200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>93700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>65200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>63800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>63700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>62400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>57900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-52600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-48600</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-40800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-40500</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-34000</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -7738,8 +7972,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7827,8 +8064,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7916,8 +8156,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8005,97 +8248,103 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-428000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-79800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-338700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-392000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-337300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>125000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-241600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-205000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>113400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>19700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-257000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-209100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-212100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-116800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-108200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-45300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-137000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>72800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>74200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-109500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1386900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-18100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1200</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8138,8 +8387,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -8183,86 +8432,89 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-21400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>57200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>19700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>20000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-54500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>36200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-320800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>281000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>51600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>27500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>35400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-30200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>28500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-9200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-137200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>143400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-96300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-297200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>427500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>4400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8270,6 +8522,9 @@
         <v>3</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
